--- a/artfynd/A 27178-2024 artfynd.xlsx
+++ b/artfynd/A 27178-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119017593</v>
       </c>
       <c r="B2" t="n">
-        <v>57308</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>119017586</v>
       </c>
       <c r="B5" t="n">
-        <v>57308</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>119017884</v>
       </c>
       <c r="B10" t="n">
-        <v>57308</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>119017675</v>
       </c>
       <c r="B12" t="n">
-        <v>57308</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 27178-2024 artfynd.xlsx
+++ b/artfynd/A 27178-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119017593</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>119017586</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>119017884</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>119017675</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
